--- a/РАБОЧИЙ СТОЛ/расчеты Останкино Сыры/Луганск/дв 01,09,26 лгрсч ост сыр.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино Сыры/Луганск/дв 01,09,26 лгрсч ост сыр.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\09,26\01,09,26 Останкино СЫРЫ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\Создание расчетов\ПОКОМ_КИ_UK_Sch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BE6DFD5-8283-404B-9EE5-7C0B26DF486F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81A7B19-5DF4-4E43-B113-1EF36C7CDFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,15 +20,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AK$43</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -433,7 +425,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -443,7 +435,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -451,9 +442,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -772,7 +761,7 @@
     <col min="11" max="12" width="7" customWidth="1"/>
     <col min="13" max="14" width="0.7109375" customWidth="1"/>
     <col min="15" max="21" width="7" customWidth="1"/>
-    <col min="22" max="23" width="7" style="19" customWidth="1"/>
+    <col min="22" max="23" width="7" style="16" customWidth="1"/>
     <col min="24" max="25" width="5" customWidth="1"/>
     <col min="26" max="35" width="6" customWidth="1"/>
     <col min="36" max="36" width="49.42578125" customWidth="1"/>
@@ -1282,8 +1271,8 @@
       </c>
       <c r="T6" s="5"/>
       <c r="U6" s="5"/>
-      <c r="V6" s="17"/>
-      <c r="W6" s="17"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
       <c r="X6" s="1">
         <f>(F6+O6+P6+S6)/Q6</f>
         <v>30.833333333333336</v>
@@ -1322,7 +1311,7 @@
       <c r="AI6" s="1">
         <v>0</v>
       </c>
-      <c r="AJ6" s="13" t="s">
+      <c r="AJ6" s="12" t="s">
         <v>37</v>
       </c>
       <c r="AK6" s="1">
@@ -1397,8 +1386,8 @@
       </c>
       <c r="T7" s="5"/>
       <c r="U7" s="5"/>
-      <c r="V7" s="17"/>
-      <c r="W7" s="17"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
       <c r="X7" s="1">
         <f t="shared" ref="X7:X43" si="5">(F7+O7+P7+S7)/Q7</f>
         <v>28.75</v>
@@ -1510,8 +1499,8 @@
       </c>
       <c r="T8" s="5"/>
       <c r="U8" s="5"/>
-      <c r="V8" s="17"/>
-      <c r="W8" s="17"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
       <c r="X8" s="1">
         <f t="shared" si="5"/>
         <v>29.411764705882355</v>
@@ -1629,10 +1618,10 @@
         <v>50</v>
       </c>
       <c r="U9" s="5"/>
-      <c r="V9" s="17">
+      <c r="V9" s="1">
         <v>50</v>
       </c>
-      <c r="W9" s="17"/>
+      <c r="W9" s="1"/>
       <c r="X9" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -1696,7 +1685,7 @@
       <c r="BA9" s="1"/>
     </row>
     <row r="10" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1736,12 +1725,12 @@
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="T10" s="20">
+      <c r="T10" s="17">
         <v>0</v>
       </c>
       <c r="U10" s="5"/>
-      <c r="V10" s="17"/>
-      <c r="W10" s="17"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
       <c r="X10" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -1805,7 +1794,7 @@
       <c r="BA10" s="1"/>
     </row>
     <row r="11" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -1845,12 +1834,12 @@
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="T11" s="20">
+      <c r="T11" s="17">
         <v>0</v>
       </c>
       <c r="U11" s="5"/>
-      <c r="V11" s="17"/>
-      <c r="W11" s="17"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
       <c r="X11" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -1960,8 +1949,8 @@
       </c>
       <c r="T12" s="5"/>
       <c r="U12" s="5"/>
-      <c r="V12" s="17"/>
-      <c r="W12" s="17"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
       <c r="X12" s="1">
         <f t="shared" si="5"/>
         <v>21.446950281906716</v>
@@ -2000,7 +1989,7 @@
       <c r="AI12" s="1">
         <v>3.2768000000000002</v>
       </c>
-      <c r="AJ12" s="15" t="s">
+      <c r="AJ12" s="14" t="s">
         <v>49</v>
       </c>
       <c r="AK12" s="1">
@@ -2073,8 +2062,8 @@
       </c>
       <c r="T13" s="5"/>
       <c r="U13" s="5"/>
-      <c r="V13" s="17"/>
-      <c r="W13" s="17"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
       <c r="X13" s="1">
         <f t="shared" si="5"/>
         <v>43</v>
@@ -2113,7 +2102,7 @@
       <c r="AI13" s="1">
         <v>2.4</v>
       </c>
-      <c r="AJ13" s="16" t="s">
+      <c r="AJ13" s="15" t="s">
         <v>47</v>
       </c>
       <c r="AK13" s="1">
@@ -2192,8 +2181,8 @@
         <v>24</v>
       </c>
       <c r="U14" s="5"/>
-      <c r="V14" s="17"/>
-      <c r="W14" s="17"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
       <c r="X14" s="1">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -2303,8 +2292,8 @@
       </c>
       <c r="T15" s="5"/>
       <c r="U15" s="5"/>
-      <c r="V15" s="17"/>
-      <c r="W15" s="17"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
       <c r="X15" s="1">
         <f t="shared" si="5"/>
         <v>65.192307692307693</v>
@@ -2343,7 +2332,7 @@
       <c r="AI15" s="1">
         <v>8</v>
       </c>
-      <c r="AJ15" s="16" t="s">
+      <c r="AJ15" s="15" t="s">
         <v>47</v>
       </c>
       <c r="AK15" s="1">
@@ -2422,8 +2411,8 @@
         <v>96</v>
       </c>
       <c r="U16" s="5"/>
-      <c r="V16" s="17"/>
-      <c r="W16" s="17"/>
+      <c r="V16" s="1"/>
+      <c r="W16" s="1"/>
       <c r="X16" s="1">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -2541,8 +2530,8 @@
         <v>48</v>
       </c>
       <c r="U17" s="5"/>
-      <c r="V17" s="17"/>
-      <c r="W17" s="17"/>
+      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
       <c r="X17" s="1">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -2656,8 +2645,8 @@
       </c>
       <c r="T18" s="5"/>
       <c r="U18" s="5"/>
-      <c r="V18" s="17"/>
-      <c r="W18" s="17"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
       <c r="X18" s="1">
         <f t="shared" si="5"/>
         <v>25.434782608695656</v>
@@ -2769,8 +2758,8 @@
       </c>
       <c r="T19" s="5"/>
       <c r="U19" s="5"/>
-      <c r="V19" s="17"/>
-      <c r="W19" s="17"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
       <c r="X19" s="1">
         <f t="shared" si="5"/>
         <v>42.878787878787882</v>
@@ -2882,8 +2871,8 @@
       </c>
       <c r="T20" s="5"/>
       <c r="U20" s="5"/>
-      <c r="V20" s="17"/>
-      <c r="W20" s="17"/>
+      <c r="V20" s="1"/>
+      <c r="W20" s="1"/>
       <c r="X20" s="1">
         <f t="shared" si="5"/>
         <v>16.323529411764707</v>
@@ -2993,8 +2982,8 @@
       </c>
       <c r="T21" s="5"/>
       <c r="U21" s="5"/>
-      <c r="V21" s="17"/>
-      <c r="W21" s="17"/>
+      <c r="V21" s="1"/>
+      <c r="W21" s="1"/>
       <c r="X21" s="1">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -3102,8 +3091,8 @@
       </c>
       <c r="T22" s="5"/>
       <c r="U22" s="5"/>
-      <c r="V22" s="17"/>
-      <c r="W22" s="17"/>
+      <c r="V22" s="1"/>
+      <c r="W22" s="1"/>
       <c r="X22" s="1">
         <f t="shared" si="5"/>
         <v>75</v>
@@ -3142,7 +3131,7 @@
       <c r="AI22" s="1">
         <v>4.5999999999999996</v>
       </c>
-      <c r="AJ22" s="16" t="s">
+      <c r="AJ22" s="15" t="s">
         <v>47</v>
       </c>
       <c r="AK22" s="1">
@@ -3167,7 +3156,7 @@
       <c r="BA22" s="1"/>
     </row>
     <row r="23" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -3214,8 +3203,8 @@
         <v>24</v>
       </c>
       <c r="U23" s="5"/>
-      <c r="V23" s="17"/>
-      <c r="W23" s="17"/>
+      <c r="V23" s="1"/>
+      <c r="W23" s="1"/>
       <c r="X23" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -3333,8 +3322,8 @@
         <v>56</v>
       </c>
       <c r="U24" s="5"/>
-      <c r="V24" s="17"/>
-      <c r="W24" s="17"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
       <c r="X24" s="1">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -3451,8 +3440,8 @@
         <f>VLOOKUP(A25,'заказ сети'!A:B,2,0)</f>
         <v>150</v>
       </c>
-      <c r="V25" s="17"/>
-      <c r="W25" s="17">
+      <c r="V25" s="1"/>
+      <c r="W25" s="1">
         <v>150</v>
       </c>
       <c r="X25" s="1">
@@ -3572,8 +3561,8 @@
         <v>130</v>
       </c>
       <c r="U26" s="5"/>
-      <c r="V26" s="17"/>
-      <c r="W26" s="17"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
       <c r="X26" s="1">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -3689,8 +3678,8 @@
         <v>40</v>
       </c>
       <c r="U27" s="5"/>
-      <c r="V27" s="17"/>
-      <c r="W27" s="17"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
       <c r="X27" s="1">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -3808,8 +3797,8 @@
         <v>60</v>
       </c>
       <c r="U28" s="5"/>
-      <c r="V28" s="17"/>
-      <c r="W28" s="17"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
       <c r="X28" s="1">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -3927,8 +3916,8 @@
         <v>160</v>
       </c>
       <c r="U29" s="5"/>
-      <c r="V29" s="17"/>
-      <c r="W29" s="17"/>
+      <c r="V29" s="1"/>
+      <c r="W29" s="1"/>
       <c r="X29" s="1">
         <f t="shared" si="5"/>
         <v>15.000000000000002</v>
@@ -4038,8 +4027,8 @@
       </c>
       <c r="T30" s="5"/>
       <c r="U30" s="5"/>
-      <c r="V30" s="17"/>
-      <c r="W30" s="17"/>
+      <c r="V30" s="1"/>
+      <c r="W30" s="1"/>
       <c r="X30" s="1">
         <f t="shared" si="5"/>
         <v>36.92307692307692</v>
@@ -4078,7 +4067,7 @@
       <c r="AI30" s="1">
         <v>11.6</v>
       </c>
-      <c r="AJ30" s="16" t="s">
+      <c r="AJ30" s="15" t="s">
         <v>47</v>
       </c>
       <c r="AK30" s="1">
@@ -4143,8 +4132,8 @@
       </c>
       <c r="T31" s="5"/>
       <c r="U31" s="5"/>
-      <c r="V31" s="17"/>
-      <c r="W31" s="17"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
       <c r="X31" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -4183,7 +4172,7 @@
       <c r="AI31" s="1">
         <v>0</v>
       </c>
-      <c r="AJ31" s="16" t="s">
+      <c r="AJ31" s="15" t="s">
         <v>47</v>
       </c>
       <c r="AK31" s="1">
@@ -4264,8 +4253,8 @@
         <v>48</v>
       </c>
       <c r="U32" s="5"/>
-      <c r="V32" s="17"/>
-      <c r="W32" s="17"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
       <c r="X32" s="1">
         <f t="shared" si="5"/>
         <v>14.999999999999998</v>
@@ -4375,8 +4364,8 @@
       </c>
       <c r="T33" s="5"/>
       <c r="U33" s="5"/>
-      <c r="V33" s="17"/>
-      <c r="W33" s="17"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
       <c r="X33" s="1">
         <f t="shared" si="5"/>
         <v>41.944444444444443</v>
@@ -4415,7 +4404,7 @@
       <c r="AI33" s="1">
         <v>8.1999999999999993</v>
       </c>
-      <c r="AJ33" s="15" t="s">
+      <c r="AJ33" s="14" t="s">
         <v>49</v>
       </c>
       <c r="AK33" s="1">
@@ -4485,8 +4474,8 @@
         <v>16</v>
       </c>
       <c r="U34" s="5"/>
-      <c r="V34" s="17"/>
-      <c r="W34" s="17"/>
+      <c r="V34" s="1"/>
+      <c r="W34" s="1"/>
       <c r="X34" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -4525,7 +4514,7 @@
       <c r="AI34" s="1">
         <v>1.3236000000000001</v>
       </c>
-      <c r="AJ34" s="14" t="s">
+      <c r="AJ34" s="13" t="s">
         <v>83</v>
       </c>
       <c r="AK34" s="1">
@@ -4598,8 +4587,8 @@
       </c>
       <c r="T35" s="5"/>
       <c r="U35" s="5"/>
-      <c r="V35" s="17"/>
-      <c r="W35" s="17"/>
+      <c r="V35" s="1"/>
+      <c r="W35" s="1"/>
       <c r="X35" s="1">
         <f t="shared" si="5"/>
         <v>29.833587122036107</v>
@@ -4638,7 +4627,7 @@
       <c r="AI35" s="1">
         <v>3.7959999999999998</v>
       </c>
-      <c r="AJ35" s="15" t="s">
+      <c r="AJ35" s="14" t="s">
         <v>49</v>
       </c>
       <c r="AK35" s="1">
@@ -4719,8 +4708,8 @@
         <v>6</v>
       </c>
       <c r="U36" s="5"/>
-      <c r="V36" s="17"/>
-      <c r="W36" s="17"/>
+      <c r="V36" s="1"/>
+      <c r="W36" s="1"/>
       <c r="X36" s="1">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -4832,8 +4821,8 @@
       </c>
       <c r="T37" s="5"/>
       <c r="U37" s="5"/>
-      <c r="V37" s="17"/>
-      <c r="W37" s="17"/>
+      <c r="V37" s="1"/>
+      <c r="W37" s="1"/>
       <c r="X37" s="1">
         <f t="shared" si="5"/>
         <v>28.913043478260871</v>
@@ -4949,8 +4938,8 @@
         <v>96</v>
       </c>
       <c r="U38" s="5"/>
-      <c r="V38" s="17"/>
-      <c r="W38" s="17"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="1"/>
       <c r="X38" s="1">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -5066,8 +5055,8 @@
         <v>210</v>
       </c>
       <c r="U39" s="5"/>
-      <c r="V39" s="17"/>
-      <c r="W39" s="17"/>
+      <c r="V39" s="1"/>
+      <c r="W39" s="1"/>
       <c r="X39" s="1">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -5179,8 +5168,8 @@
       </c>
       <c r="T40" s="5"/>
       <c r="U40" s="5"/>
-      <c r="V40" s="17"/>
-      <c r="W40" s="17"/>
+      <c r="V40" s="1"/>
+      <c r="W40" s="1"/>
       <c r="X40" s="1">
         <f t="shared" si="5"/>
         <v>15.307299890683831</v>
@@ -5290,8 +5279,8 @@
       </c>
       <c r="T41" s="5"/>
       <c r="U41" s="5"/>
-      <c r="V41" s="17"/>
-      <c r="W41" s="17"/>
+      <c r="V41" s="1"/>
+      <c r="W41" s="1"/>
       <c r="X41" s="1">
         <f t="shared" si="5"/>
         <v>17.283950617283953</v>
@@ -5330,7 +5319,7 @@
       <c r="AI41" s="1">
         <v>15</v>
       </c>
-      <c r="AJ41" s="15" t="s">
+      <c r="AJ41" s="14" t="s">
         <v>49</v>
       </c>
       <c r="AK41" s="1">
@@ -5355,91 +5344,91 @@
       <c r="BA41" s="1"/>
     </row>
     <row r="42" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="10">
+      <c r="C42" s="9">
         <v>-3</v>
       </c>
-      <c r="D42" s="10">
+      <c r="D42" s="9">
         <v>3</v>
       </c>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="11">
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="10">
         <v>0</v>
       </c>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10" t="s">
+      <c r="H42" s="9"/>
+      <c r="I42" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="J42" s="10" t="s">
+      <c r="J42" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10">
+      <c r="K42" s="9"/>
+      <c r="L42" s="9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M42" s="10"/>
-      <c r="N42" s="10"/>
-      <c r="O42" s="10"/>
-      <c r="P42" s="10"/>
-      <c r="Q42" s="10">
+      <c r="M42" s="9"/>
+      <c r="N42" s="9"/>
+      <c r="O42" s="9"/>
+      <c r="P42" s="9"/>
+      <c r="Q42" s="9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R42" s="12"/>
+      <c r="R42" s="11"/>
       <c r="S42" s="5">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="T42" s="5"/>
       <c r="U42" s="5"/>
-      <c r="V42" s="18"/>
-      <c r="W42" s="18"/>
+      <c r="V42" s="9"/>
+      <c r="W42" s="9"/>
       <c r="X42" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y42" s="10" t="e">
+      <c r="Y42" s="9" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z42" s="10">
+      <c r="Z42" s="9">
         <v>0</v>
       </c>
-      <c r="AA42" s="10">
+      <c r="AA42" s="9">
         <v>0</v>
       </c>
-      <c r="AB42" s="10">
+      <c r="AB42" s="9">
         <v>0</v>
       </c>
-      <c r="AC42" s="10">
+      <c r="AC42" s="9">
         <v>0.6</v>
       </c>
-      <c r="AD42" s="10">
+      <c r="AD42" s="9">
         <v>0</v>
       </c>
-      <c r="AE42" s="10">
+      <c r="AE42" s="9">
         <v>0</v>
       </c>
-      <c r="AF42" s="10">
+      <c r="AF42" s="9">
         <v>0</v>
       </c>
-      <c r="AG42" s="10">
+      <c r="AG42" s="9">
         <v>0</v>
       </c>
-      <c r="AH42" s="10">
+      <c r="AH42" s="9">
         <v>0</v>
       </c>
-      <c r="AI42" s="10">
+      <c r="AI42" s="9">
         <v>0</v>
       </c>
-      <c r="AJ42" s="10"/>
+      <c r="AJ42" s="9"/>
       <c r="AK42" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -5508,8 +5497,8 @@
       </c>
       <c r="T43" s="5"/>
       <c r="U43" s="5"/>
-      <c r="V43" s="17"/>
-      <c r="W43" s="17"/>
+      <c r="V43" s="1"/>
+      <c r="W43" s="1"/>
       <c r="X43" s="1">
         <f t="shared" si="5"/>
         <v>19.127215485074629</v>
@@ -5548,7 +5537,7 @@
       <c r="AI43" s="1">
         <v>2.9496000000000002</v>
       </c>
-      <c r="AJ43" s="15" t="s">
+      <c r="AJ43" s="14" t="s">
         <v>49</v>
       </c>
       <c r="AK43" s="1">
